--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ166"/>
+  <dimension ref="A1:AZ167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3143,48 +3143,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117613645</v>
+        <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>81312</v>
+        <v>92701</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skirträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619553</v>
+        <v>619626</v>
       </c>
       <c r="R24" t="n">
-        <v>7215972</v>
+        <v>7216136</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,22 +3208,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,22 +3233,22 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613645</t>
+          <t>https://artportalen.se/Sighting/137152785</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117613590</v>
+        <v>117613645</v>
       </c>
       <c r="B25" t="n">
-        <v>91909</v>
+        <v>81312</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,21 +3256,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3290,10 +3280,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619529</v>
+        <v>619553</v>
       </c>
       <c r="R25" t="n">
-        <v>7215800</v>
+        <v>7215972</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3325,7 +3315,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3335,7 +3325,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3361,13 +3351,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613590</t>
+          <t>https://artportalen.se/Sighting/117613645</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117613594</v>
+        <v>117613590</v>
       </c>
       <c r="B26" t="n">
         <v>91909</v>
@@ -3402,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619617</v>
+        <v>619529</v>
       </c>
       <c r="R26" t="n">
-        <v>7215806</v>
+        <v>7215800</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3437,7 +3427,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3447,7 +3437,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,13 +3463,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613594</t>
+          <t>https://artportalen.se/Sighting/117613590</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117613608</v>
+        <v>117613594</v>
       </c>
       <c r="B27" t="n">
         <v>91909</v>
@@ -3514,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619551</v>
+        <v>619617</v>
       </c>
       <c r="R27" t="n">
-        <v>7215843</v>
+        <v>7215806</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3549,7 +3539,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3549,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3585,13 +3575,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613608</t>
+          <t>https://artportalen.se/Sighting/117613594</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117613624</v>
+        <v>117613608</v>
       </c>
       <c r="B28" t="n">
         <v>91909</v>
@@ -3626,10 +3616,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619556</v>
+        <v>619551</v>
       </c>
       <c r="R28" t="n">
-        <v>7215859</v>
+        <v>7215843</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3661,7 +3651,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3671,7 +3661,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3697,13 +3687,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613624</t>
+          <t>https://artportalen.se/Sighting/117613608</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117613655</v>
+        <v>117613624</v>
       </c>
       <c r="B29" t="n">
         <v>91909</v>
@@ -3738,10 +3728,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619561</v>
+        <v>619556</v>
       </c>
       <c r="R29" t="n">
-        <v>7215911</v>
+        <v>7215859</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3773,7 +3763,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3783,7 +3773,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3809,13 +3799,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613655</t>
+          <t>https://artportalen.se/Sighting/117613624</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117613659</v>
+        <v>117613655</v>
       </c>
       <c r="B30" t="n">
         <v>91909</v>
@@ -3850,10 +3840,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619577</v>
+        <v>619561</v>
       </c>
       <c r="R30" t="n">
-        <v>7215927</v>
+        <v>7215911</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3885,7 +3875,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3895,7 +3885,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3921,13 +3911,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613659</t>
+          <t>https://artportalen.se/Sighting/117613655</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117613661</v>
+        <v>117613659</v>
       </c>
       <c r="B31" t="n">
         <v>91909</v>
@@ -3962,10 +3952,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>619574</v>
+        <v>619577</v>
       </c>
       <c r="R31" t="n">
-        <v>7215938</v>
+        <v>7215927</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,13 +4023,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613661</t>
+          <t>https://artportalen.se/Sighting/117613659</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117613739</v>
+        <v>117613661</v>
       </c>
       <c r="B32" t="n">
         <v>91909</v>
@@ -4074,10 +4064,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619573</v>
+        <v>619574</v>
       </c>
       <c r="R32" t="n">
-        <v>7215805</v>
+        <v>7215938</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4109,7 +4099,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,7 +4109,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,13 +4135,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613739</t>
+          <t>https://artportalen.se/Sighting/117613661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117613747</v>
+        <v>117613739</v>
       </c>
       <c r="B33" t="n">
         <v>91909</v>
@@ -4186,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>619574</v>
+        <v>619573</v>
       </c>
       <c r="R33" t="n">
-        <v>7215791</v>
+        <v>7215805</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4221,7 +4211,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4231,7 +4221,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4257,13 +4247,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613747</t>
+          <t>https://artportalen.se/Sighting/117613739</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117613749</v>
+        <v>117613747</v>
       </c>
       <c r="B34" t="n">
         <v>91909</v>
@@ -4298,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619577</v>
+        <v>619574</v>
       </c>
       <c r="R34" t="n">
-        <v>7215786</v>
+        <v>7215791</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4369,13 +4359,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613749</t>
+          <t>https://artportalen.se/Sighting/117613747</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117613751</v>
+        <v>117613749</v>
       </c>
       <c r="B35" t="n">
         <v>91909</v>
@@ -4410,10 +4400,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619563</v>
+        <v>619577</v>
       </c>
       <c r="R35" t="n">
-        <v>7215782</v>
+        <v>7215786</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4445,7 +4435,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4455,7 +4445,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4481,38 +4471,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613751</t>
+          <t>https://artportalen.se/Sighting/117613749</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117613589</v>
+        <v>117613751</v>
       </c>
       <c r="B36" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4522,10 +4512,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>619522</v>
+        <v>619563</v>
       </c>
       <c r="R36" t="n">
-        <v>7215799</v>
+        <v>7215782</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4557,7 +4547,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4567,7 +4557,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4593,38 +4583,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613589</t>
+          <t>https://artportalen.se/Sighting/117613751</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117613750</v>
+        <v>117613589</v>
       </c>
       <c r="B37" t="n">
-        <v>92369</v>
+        <v>91923</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4634,10 +4624,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619556</v>
+        <v>619522</v>
       </c>
       <c r="R37" t="n">
-        <v>7215782</v>
+        <v>7215799</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4669,7 +4659,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4679,7 +4669,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4705,38 +4695,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613750</t>
+          <t>https://artportalen.se/Sighting/117613589</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117613670</v>
+        <v>117613750</v>
       </c>
       <c r="B38" t="n">
-        <v>101299</v>
+        <v>92369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1365</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4746,10 +4736,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>619632</v>
+        <v>619556</v>
       </c>
       <c r="R38" t="n">
-        <v>7215967</v>
+        <v>7215782</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4781,7 +4771,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4791,7 +4781,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4817,13 +4807,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613670</t>
+          <t>https://artportalen.se/Sighting/117613750</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117613671</v>
+        <v>117613670</v>
       </c>
       <c r="B39" t="n">
         <v>101299</v>
@@ -4858,10 +4848,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>619629</v>
+        <v>619632</v>
       </c>
       <c r="R39" t="n">
-        <v>7215970</v>
+        <v>7215967</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4929,13 +4919,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613671</t>
+          <t>https://artportalen.se/Sighting/117613670</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117613674</v>
+        <v>117613671</v>
       </c>
       <c r="B40" t="n">
         <v>101299</v>
@@ -4970,10 +4960,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619867</v>
+        <v>619629</v>
       </c>
       <c r="R40" t="n">
-        <v>7215947</v>
+        <v>7215970</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5005,7 +4995,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5015,7 +5005,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5041,13 +5031,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613674</t>
+          <t>https://artportalen.se/Sighting/117613671</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117613675</v>
+        <v>117613674</v>
       </c>
       <c r="B41" t="n">
         <v>101299</v>
@@ -5082,10 +5072,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619866</v>
+        <v>619867</v>
       </c>
       <c r="R41" t="n">
-        <v>7215946</v>
+        <v>7215947</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5153,13 +5143,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613675</t>
+          <t>https://artportalen.se/Sighting/117613674</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117613676</v>
+        <v>117613675</v>
       </c>
       <c r="B42" t="n">
         <v>101299</v>
@@ -5194,10 +5184,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619870</v>
+        <v>619866</v>
       </c>
       <c r="R42" t="n">
-        <v>7215940</v>
+        <v>7215946</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5265,13 +5255,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613676</t>
+          <t>https://artportalen.se/Sighting/117613675</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117613677</v>
+        <v>117613676</v>
       </c>
       <c r="B43" t="n">
         <v>101299</v>
@@ -5306,10 +5296,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>619887</v>
+        <v>619870</v>
       </c>
       <c r="R43" t="n">
-        <v>7215924</v>
+        <v>7215940</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5341,7 +5331,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5351,7 +5341,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5377,13 +5367,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613677</t>
+          <t>https://artportalen.se/Sighting/117613676</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117613678</v>
+        <v>117613677</v>
       </c>
       <c r="B44" t="n">
         <v>101299</v>
@@ -5418,10 +5408,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619893</v>
+        <v>619887</v>
       </c>
       <c r="R44" t="n">
-        <v>7215927</v>
+        <v>7215924</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5489,13 +5479,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613678</t>
+          <t>https://artportalen.se/Sighting/117613677</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117613679</v>
+        <v>117613678</v>
       </c>
       <c r="B45" t="n">
         <v>101299</v>
@@ -5530,10 +5520,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>619900</v>
+        <v>619893</v>
       </c>
       <c r="R45" t="n">
-        <v>7215930</v>
+        <v>7215927</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5601,13 +5591,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613679</t>
+          <t>https://artportalen.se/Sighting/117613678</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117613680</v>
+        <v>117613679</v>
       </c>
       <c r="B46" t="n">
         <v>101299</v>
@@ -5642,7 +5632,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>619905</v>
+        <v>619900</v>
       </c>
       <c r="R46" t="n">
         <v>7215930</v>
@@ -5713,13 +5703,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613680</t>
+          <t>https://artportalen.se/Sighting/117613679</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117613681</v>
+        <v>117613680</v>
       </c>
       <c r="B47" t="n">
         <v>101299</v>
@@ -5754,10 +5744,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>619909</v>
+        <v>619905</v>
       </c>
       <c r="R47" t="n">
-        <v>7215922</v>
+        <v>7215930</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5789,7 +5779,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5799,7 +5789,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5825,13 +5815,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613681</t>
+          <t>https://artportalen.se/Sighting/117613680</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120472131</v>
+        <v>117613681</v>
       </c>
       <c r="B48" t="n">
         <v>101299</v>
@@ -5866,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>619880</v>
+        <v>619909</v>
       </c>
       <c r="R48" t="n">
-        <v>7215932</v>
+        <v>7215922</v>
       </c>
       <c r="S48" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5894,19 +5884,24 @@
           <t>Stensele</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>AC-Sto-0200</t>
-        </is>
-      </c>
       <c r="Y48" t="inlineStr">
         <is>
           <t>2024-06-06</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5921,7 +5916,7 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -5929,45 +5924,41 @@
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120472131</t>
+          <t>https://artportalen.se/Sighting/117613681</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117613653</v>
+        <v>120472131</v>
       </c>
       <c r="B49" t="n">
-        <v>92281</v>
+        <v>101299</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2062</v>
+        <v>1365</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5977,13 +5968,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>619564</v>
+        <v>619880</v>
       </c>
       <c r="R49" t="n">
-        <v>7215908</v>
+        <v>7215932</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6005,24 +5996,19 @@
           <t>Stensele</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>AC-Sto-0200</t>
+        </is>
+      </c>
       <c r="Y49" t="inlineStr">
         <is>
           <t>2024-06-06</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6037,7 +6023,7 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -6045,41 +6031,45 @@
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613653</t>
+          <t>https://artportalen.se/Sighting/120472131</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117613610</v>
+        <v>117613653</v>
       </c>
       <c r="B50" t="n">
-        <v>80433</v>
+        <v>92281</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>2062</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6089,10 +6079,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619566</v>
+        <v>619564</v>
       </c>
       <c r="R50" t="n">
-        <v>7215850</v>
+        <v>7215908</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6124,7 +6114,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6134,7 +6124,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6160,13 +6150,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613610</t>
+          <t>https://artportalen.se/Sighting/117613653</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117613621</v>
+        <v>117613610</v>
       </c>
       <c r="B51" t="n">
         <v>80433</v>
@@ -6201,10 +6191,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619562</v>
+        <v>619566</v>
       </c>
       <c r="R51" t="n">
-        <v>7215861</v>
+        <v>7215850</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6236,7 +6226,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6246,7 +6236,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6272,13 +6262,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613621</t>
+          <t>https://artportalen.se/Sighting/117613610</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117613646</v>
+        <v>117613621</v>
       </c>
       <c r="B52" t="n">
         <v>80433</v>
@@ -6313,10 +6303,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>619566</v>
+        <v>619562</v>
       </c>
       <c r="R52" t="n">
-        <v>7215964</v>
+        <v>7215861</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6348,7 +6338,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6358,7 +6348,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6384,13 +6374,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613646</t>
+          <t>https://artportalen.se/Sighting/117613621</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117613727</v>
+        <v>117613646</v>
       </c>
       <c r="B53" t="n">
         <v>80433</v>
@@ -6425,10 +6415,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619625</v>
+        <v>619566</v>
       </c>
       <c r="R53" t="n">
-        <v>7215804</v>
+        <v>7215964</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6460,7 +6450,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6470,7 +6460,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6496,38 +6486,38 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613727</t>
+          <t>https://artportalen.se/Sighting/117613646</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117613615</v>
+        <v>117613727</v>
       </c>
       <c r="B54" t="n">
-        <v>91872</v>
+        <v>80433</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6537,10 +6527,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>619582</v>
+        <v>619625</v>
       </c>
       <c r="R54" t="n">
-        <v>7215879</v>
+        <v>7215804</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6572,7 +6562,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6582,7 +6572,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6608,13 +6598,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613615</t>
+          <t>https://artportalen.se/Sighting/117613727</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117613669</v>
+        <v>117613615</v>
       </c>
       <c r="B55" t="n">
         <v>91872</v>
@@ -6649,10 +6639,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>619631</v>
+        <v>619582</v>
       </c>
       <c r="R55" t="n">
-        <v>7215964</v>
+        <v>7215879</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6684,7 +6674,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6694,7 +6684,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,38 +6710,38 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613669</t>
+          <t>https://artportalen.se/Sighting/117613615</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117613599</v>
+        <v>117613669</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6761,10 +6751,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>619602</v>
+        <v>619631</v>
       </c>
       <c r="R56" t="n">
-        <v>7215855</v>
+        <v>7215964</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6796,7 +6786,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6806,7 +6796,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6832,13 +6822,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613599</t>
+          <t>https://artportalen.se/Sighting/117613669</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117613614</v>
+        <v>117613599</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6873,10 +6863,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>619579</v>
+        <v>619602</v>
       </c>
       <c r="R57" t="n">
-        <v>7215872</v>
+        <v>7215855</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6908,7 +6898,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6918,7 +6908,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6944,13 +6934,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613614</t>
+          <t>https://artportalen.se/Sighting/117613599</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117613619</v>
+        <v>117613614</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -6985,10 +6975,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>619572</v>
+        <v>619579</v>
       </c>
       <c r="R58" t="n">
-        <v>7215883</v>
+        <v>7215872</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7020,7 +7010,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7030,7 +7020,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7056,13 +7046,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613619</t>
+          <t>https://artportalen.se/Sighting/117613614</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117613627</v>
+        <v>117613619</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -7097,10 +7087,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>619561</v>
+        <v>619572</v>
       </c>
       <c r="R59" t="n">
-        <v>7215877</v>
+        <v>7215883</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7132,7 +7122,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7142,7 +7132,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7168,13 +7158,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613627</t>
+          <t>https://artportalen.se/Sighting/117613619</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117613654</v>
+        <v>117613627</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -7209,10 +7199,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619565</v>
+        <v>619561</v>
       </c>
       <c r="R60" t="n">
-        <v>7215909</v>
+        <v>7215877</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7244,7 +7234,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7254,7 +7244,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7280,13 +7270,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613654</t>
+          <t>https://artportalen.se/Sighting/117613627</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117613745</v>
+        <v>117613654</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -7321,10 +7311,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>619575</v>
+        <v>619565</v>
       </c>
       <c r="R61" t="n">
-        <v>7215781</v>
+        <v>7215909</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7356,7 +7346,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7366,7 +7356,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7392,38 +7382,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613745</t>
+          <t>https://artportalen.se/Sighting/117613654</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117613618</v>
+        <v>117613745</v>
       </c>
       <c r="B62" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7433,10 +7423,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>619564</v>
+        <v>619575</v>
       </c>
       <c r="R62" t="n">
-        <v>7215885</v>
+        <v>7215781</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7468,7 +7458,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7478,7 +7468,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7504,16 +7494,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613618</t>
+          <t>https://artportalen.se/Sighting/117613745</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117613673</v>
+        <v>117613618</v>
       </c>
       <c r="B63" t="n">
-        <v>79946</v>
+        <v>83307</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7521,21 +7511,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7545,10 +7535,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>619743</v>
+        <v>619564</v>
       </c>
       <c r="R63" t="n">
-        <v>7215970</v>
+        <v>7215885</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7580,7 +7570,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7590,7 +7580,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7616,13 +7606,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613673</t>
+          <t>https://artportalen.se/Sighting/117613618</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117613769</v>
+        <v>117613673</v>
       </c>
       <c r="B64" t="n">
         <v>79946</v>
@@ -7657,10 +7647,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619534</v>
+        <v>619743</v>
       </c>
       <c r="R64" t="n">
-        <v>7215765</v>
+        <v>7215970</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7692,7 +7682,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7702,7 +7692,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7728,13 +7718,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613769</t>
+          <t>https://artportalen.se/Sighting/117613673</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117613770</v>
+        <v>117613769</v>
       </c>
       <c r="B65" t="n">
         <v>79946</v>
@@ -7769,10 +7759,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619533</v>
+        <v>619534</v>
       </c>
       <c r="R65" t="n">
-        <v>7215755</v>
+        <v>7215765</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7804,7 +7794,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7814,7 +7804,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7840,38 +7830,38 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613770</t>
+          <t>https://artportalen.se/Sighting/117613769</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117613616</v>
+        <v>117613770</v>
       </c>
       <c r="B66" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7881,10 +7871,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>619584</v>
+        <v>619533</v>
       </c>
       <c r="R66" t="n">
-        <v>7215892</v>
+        <v>7215755</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7916,7 +7906,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7926,7 +7916,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7952,13 +7942,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613616</t>
+          <t>https://artportalen.se/Sighting/117613770</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117613764</v>
+        <v>117613616</v>
       </c>
       <c r="B67" t="n">
         <v>80336</v>
@@ -7993,10 +7983,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619563</v>
+        <v>619584</v>
       </c>
       <c r="R67" t="n">
-        <v>7215746</v>
+        <v>7215892</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8028,7 +8018,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8038,7 +8028,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8064,38 +8054,38 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613764</t>
+          <t>https://artportalen.se/Sighting/117613616</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117613593</v>
+        <v>117613764</v>
       </c>
       <c r="B68" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8105,10 +8095,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>619544</v>
+        <v>619563</v>
       </c>
       <c r="R68" t="n">
-        <v>7215797</v>
+        <v>7215746</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8140,7 +8130,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8150,7 +8140,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8176,13 +8166,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613593</t>
+          <t>https://artportalen.se/Sighting/117613764</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117613601</v>
+        <v>117613593</v>
       </c>
       <c r="B69" t="n">
         <v>80432</v>
@@ -8217,10 +8207,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619575</v>
+        <v>619544</v>
       </c>
       <c r="R69" t="n">
-        <v>7215827</v>
+        <v>7215797</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8252,7 +8242,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8262,7 +8252,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8288,13 +8278,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613601</t>
+          <t>https://artportalen.se/Sighting/117613593</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117613611</v>
+        <v>117613601</v>
       </c>
       <c r="B70" t="n">
         <v>80432</v>
@@ -8329,10 +8319,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>619568</v>
+        <v>619575</v>
       </c>
       <c r="R70" t="n">
-        <v>7215856</v>
+        <v>7215827</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8364,7 +8354,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8374,7 +8364,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8400,13 +8390,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613611</t>
+          <t>https://artportalen.se/Sighting/117613601</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117613613</v>
+        <v>117613611</v>
       </c>
       <c r="B71" t="n">
         <v>80432</v>
@@ -8441,10 +8431,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619567</v>
+        <v>619568</v>
       </c>
       <c r="R71" t="n">
-        <v>7215864</v>
+        <v>7215856</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8476,7 +8466,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8486,7 +8476,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8512,13 +8502,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613613</t>
+          <t>https://artportalen.se/Sighting/117613611</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117613622</v>
+        <v>117613613</v>
       </c>
       <c r="B72" t="n">
         <v>80432</v>
@@ -8553,10 +8543,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>619562</v>
+        <v>619567</v>
       </c>
       <c r="R72" t="n">
-        <v>7215860</v>
+        <v>7215864</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8588,7 +8578,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8598,7 +8588,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8624,13 +8614,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613622</t>
+          <t>https://artportalen.se/Sighting/117613613</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117613631</v>
+        <v>117613622</v>
       </c>
       <c r="B73" t="n">
         <v>80432</v>
@@ -8665,10 +8655,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619539</v>
+        <v>619562</v>
       </c>
       <c r="R73" t="n">
-        <v>7215859</v>
+        <v>7215860</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8700,7 +8690,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8710,7 +8700,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8736,13 +8726,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613631</t>
+          <t>https://artportalen.se/Sighting/117613622</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117613633</v>
+        <v>117613631</v>
       </c>
       <c r="B74" t="n">
         <v>80432</v>
@@ -8777,10 +8767,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619556</v>
+        <v>619539</v>
       </c>
       <c r="R74" t="n">
-        <v>7215883</v>
+        <v>7215859</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8812,7 +8802,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8822,7 +8812,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8848,13 +8838,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613633</t>
+          <t>https://artportalen.se/Sighting/117613631</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117613635</v>
+        <v>117613633</v>
       </c>
       <c r="B75" t="n">
         <v>80432</v>
@@ -8889,10 +8879,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>619516</v>
+        <v>619556</v>
       </c>
       <c r="R75" t="n">
-        <v>7215928</v>
+        <v>7215883</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8924,7 +8914,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8934,7 +8924,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8960,13 +8950,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613635</t>
+          <t>https://artportalen.se/Sighting/117613633</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117613638</v>
+        <v>117613635</v>
       </c>
       <c r="B76" t="n">
         <v>80432</v>
@@ -9001,10 +8991,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>619503</v>
+        <v>619516</v>
       </c>
       <c r="R76" t="n">
-        <v>7215952</v>
+        <v>7215928</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9036,7 +9026,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9046,7 +9036,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9072,13 +9062,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613638</t>
+          <t>https://artportalen.se/Sighting/117613635</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117613639</v>
+        <v>117613638</v>
       </c>
       <c r="B77" t="n">
         <v>80432</v>
@@ -9113,10 +9103,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619498</v>
+        <v>619503</v>
       </c>
       <c r="R77" t="n">
-        <v>7215953</v>
+        <v>7215952</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9184,13 +9174,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613639</t>
+          <t>https://artportalen.se/Sighting/117613638</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117613640</v>
+        <v>117613639</v>
       </c>
       <c r="B78" t="n">
         <v>80432</v>
@@ -9225,10 +9215,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619508</v>
+        <v>619498</v>
       </c>
       <c r="R78" t="n">
-        <v>7215964</v>
+        <v>7215953</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9260,7 +9250,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9270,7 +9260,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9296,13 +9286,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613640</t>
+          <t>https://artportalen.se/Sighting/117613639</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117613642</v>
+        <v>117613640</v>
       </c>
       <c r="B79" t="n">
         <v>80432</v>
@@ -9337,10 +9327,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>619510</v>
+        <v>619508</v>
       </c>
       <c r="R79" t="n">
-        <v>7215959</v>
+        <v>7215964</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9372,7 +9362,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9382,7 +9372,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9408,13 +9398,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613642</t>
+          <t>https://artportalen.se/Sighting/117613640</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117613648</v>
+        <v>117613642</v>
       </c>
       <c r="B80" t="n">
         <v>80432</v>
@@ -9449,10 +9439,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619566</v>
+        <v>619510</v>
       </c>
       <c r="R80" t="n">
-        <v>7215964</v>
+        <v>7215959</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9484,7 +9474,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9494,7 +9484,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9520,13 +9510,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613648</t>
+          <t>https://artportalen.se/Sighting/117613642</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117613651</v>
+        <v>117613648</v>
       </c>
       <c r="B81" t="n">
         <v>80432</v>
@@ -9561,10 +9551,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619553</v>
+        <v>619566</v>
       </c>
       <c r="R81" t="n">
-        <v>7215913</v>
+        <v>7215964</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9596,7 +9586,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9606,7 +9596,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9632,13 +9622,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613651</t>
+          <t>https://artportalen.se/Sighting/117613648</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117613715</v>
+        <v>117613651</v>
       </c>
       <c r="B82" t="n">
         <v>80432</v>
@@ -9673,10 +9663,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619687</v>
+        <v>619553</v>
       </c>
       <c r="R82" t="n">
-        <v>7215793</v>
+        <v>7215913</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9708,7 +9698,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9718,7 +9708,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9744,13 +9734,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613715</t>
+          <t>https://artportalen.se/Sighting/117613651</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117613722</v>
+        <v>117613715</v>
       </c>
       <c r="B83" t="n">
         <v>80432</v>
@@ -9785,10 +9775,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>619658</v>
+        <v>619687</v>
       </c>
       <c r="R83" t="n">
-        <v>7215775</v>
+        <v>7215793</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9820,7 +9810,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9830,7 +9820,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9856,13 +9846,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613722</t>
+          <t>https://artportalen.se/Sighting/117613715</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117613724</v>
+        <v>117613722</v>
       </c>
       <c r="B84" t="n">
         <v>80432</v>
@@ -9897,10 +9887,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>619653</v>
+        <v>619658</v>
       </c>
       <c r="R84" t="n">
-        <v>7215780</v>
+        <v>7215775</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9932,7 +9922,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9942,7 +9932,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9968,13 +9958,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613724</t>
+          <t>https://artportalen.se/Sighting/117613722</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117613725</v>
+        <v>117613724</v>
       </c>
       <c r="B85" t="n">
         <v>80432</v>
@@ -10009,10 +9999,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>619628</v>
+        <v>619653</v>
       </c>
       <c r="R85" t="n">
-        <v>7215792</v>
+        <v>7215780</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10044,7 +10034,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10054,7 +10044,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10080,13 +10070,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613725</t>
+          <t>https://artportalen.se/Sighting/117613724</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117613728</v>
+        <v>117613725</v>
       </c>
       <c r="B86" t="n">
         <v>80432</v>
@@ -10121,10 +10111,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>619621</v>
+        <v>619628</v>
       </c>
       <c r="R86" t="n">
-        <v>7215805</v>
+        <v>7215792</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10156,7 +10146,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10166,7 +10156,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10192,13 +10182,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613728</t>
+          <t>https://artportalen.se/Sighting/117613725</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117613731</v>
+        <v>117613728</v>
       </c>
       <c r="B87" t="n">
         <v>80432</v>
@@ -10233,10 +10223,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>619611</v>
+        <v>619621</v>
       </c>
       <c r="R87" t="n">
-        <v>7215810</v>
+        <v>7215805</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10268,7 +10258,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10278,7 +10268,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10304,13 +10294,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613731</t>
+          <t>https://artportalen.se/Sighting/117613728</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117613735</v>
+        <v>117613731</v>
       </c>
       <c r="B88" t="n">
         <v>80432</v>
@@ -10345,10 +10335,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>619601</v>
+        <v>619611</v>
       </c>
       <c r="R88" t="n">
-        <v>7215813</v>
+        <v>7215810</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10380,7 +10370,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10390,7 +10380,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10416,13 +10406,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613735</t>
+          <t>https://artportalen.se/Sighting/117613731</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117613737</v>
+        <v>117613735</v>
       </c>
       <c r="B89" t="n">
         <v>80432</v>
@@ -10457,10 +10447,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>619598</v>
+        <v>619601</v>
       </c>
       <c r="R89" t="n">
-        <v>7215806</v>
+        <v>7215813</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10492,7 +10482,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10502,7 +10492,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10528,13 +10518,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613737</t>
+          <t>https://artportalen.se/Sighting/117613735</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117613761</v>
+        <v>117613737</v>
       </c>
       <c r="B90" t="n">
         <v>80432</v>
@@ -10569,10 +10559,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>619585</v>
+        <v>619598</v>
       </c>
       <c r="R90" t="n">
-        <v>7215746</v>
+        <v>7215806</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10604,7 +10594,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10614,7 +10604,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10640,13 +10630,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613761</t>
+          <t>https://artportalen.se/Sighting/117613737</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117613766</v>
+        <v>117613761</v>
       </c>
       <c r="B91" t="n">
         <v>80432</v>
@@ -10681,10 +10671,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>619564</v>
+        <v>619585</v>
       </c>
       <c r="R91" t="n">
-        <v>7215745</v>
+        <v>7215746</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10716,7 +10706,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10726,7 +10716,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10752,38 +10742,38 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613766</t>
+          <t>https://artportalen.se/Sighting/117613761</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117613637</v>
+        <v>117613766</v>
       </c>
       <c r="B92" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10793,10 +10783,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>619504</v>
+        <v>619564</v>
       </c>
       <c r="R92" t="n">
-        <v>7215950</v>
+        <v>7215745</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10828,7 +10818,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10838,7 +10828,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10864,13 +10854,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613637</t>
+          <t>https://artportalen.se/Sighting/117613766</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117613644</v>
+        <v>117613637</v>
       </c>
       <c r="B93" t="n">
         <v>80461</v>
@@ -10905,10 +10895,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>619512</v>
+        <v>619504</v>
       </c>
       <c r="R93" t="n">
-        <v>7215959</v>
+        <v>7215950</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10940,7 +10930,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10950,7 +10940,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10976,13 +10966,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613644</t>
+          <t>https://artportalen.se/Sighting/117613637</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117613652</v>
+        <v>117613644</v>
       </c>
       <c r="B94" t="n">
         <v>80461</v>
@@ -11017,10 +11007,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>619553</v>
+        <v>619512</v>
       </c>
       <c r="R94" t="n">
-        <v>7215913</v>
+        <v>7215959</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11052,7 +11042,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11062,7 +11052,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11088,13 +11078,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613652</t>
+          <t>https://artportalen.se/Sighting/117613644</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117613726</v>
+        <v>117613652</v>
       </c>
       <c r="B95" t="n">
         <v>80461</v>
@@ -11129,10 +11119,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>619625</v>
+        <v>619553</v>
       </c>
       <c r="R95" t="n">
-        <v>7215794</v>
+        <v>7215913</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11164,7 +11154,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11174,7 +11164,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11200,13 +11190,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613726</t>
+          <t>https://artportalen.se/Sighting/117613652</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117613729</v>
+        <v>117613726</v>
       </c>
       <c r="B96" t="n">
         <v>80461</v>
@@ -11241,10 +11231,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>619621</v>
+        <v>619625</v>
       </c>
       <c r="R96" t="n">
-        <v>7215805</v>
+        <v>7215794</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11276,7 +11266,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11286,7 +11276,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11312,13 +11302,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613729</t>
+          <t>https://artportalen.se/Sighting/117613726</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117613733</v>
+        <v>117613729</v>
       </c>
       <c r="B97" t="n">
         <v>80461</v>
@@ -11353,10 +11343,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>619610</v>
+        <v>619621</v>
       </c>
       <c r="R97" t="n">
-        <v>7215807</v>
+        <v>7215805</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11388,7 +11378,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11398,7 +11388,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11424,13 +11414,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613733</t>
+          <t>https://artportalen.se/Sighting/117613729</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117613736</v>
+        <v>117613733</v>
       </c>
       <c r="B98" t="n">
         <v>80461</v>
@@ -11465,10 +11455,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>619601</v>
+        <v>619610</v>
       </c>
       <c r="R98" t="n">
-        <v>7215813</v>
+        <v>7215807</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11500,7 +11490,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11510,7 +11500,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11536,13 +11526,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613736</t>
+          <t>https://artportalen.se/Sighting/117613733</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117613765</v>
+        <v>117613736</v>
       </c>
       <c r="B99" t="n">
         <v>80461</v>
@@ -11577,10 +11567,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>619563</v>
+        <v>619601</v>
       </c>
       <c r="R99" t="n">
-        <v>7215746</v>
+        <v>7215813</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11612,7 +11602,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11622,7 +11612,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11648,16 +11638,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613765</t>
+          <t>https://artportalen.se/Sighting/117613736</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117613612</v>
+        <v>117613765</v>
       </c>
       <c r="B100" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11665,21 +11655,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11689,10 +11679,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>619568</v>
+        <v>619563</v>
       </c>
       <c r="R100" t="n">
-        <v>7215856</v>
+        <v>7215746</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11724,7 +11714,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11734,7 +11724,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11760,13 +11750,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613612</t>
+          <t>https://artportalen.se/Sighting/117613765</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117613632</v>
+        <v>117613612</v>
       </c>
       <c r="B101" t="n">
         <v>80467</v>
@@ -11801,10 +11791,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>619539</v>
+        <v>619568</v>
       </c>
       <c r="R101" t="n">
-        <v>7215859</v>
+        <v>7215856</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11836,7 +11826,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11846,7 +11836,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11872,13 +11862,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613632</t>
+          <t>https://artportalen.se/Sighting/117613612</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117613634</v>
+        <v>117613632</v>
       </c>
       <c r="B102" t="n">
         <v>80467</v>
@@ -11913,10 +11903,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>619557</v>
+        <v>619539</v>
       </c>
       <c r="R102" t="n">
-        <v>7215881</v>
+        <v>7215859</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11948,7 +11938,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11958,7 +11948,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11984,13 +11974,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613634</t>
+          <t>https://artportalen.se/Sighting/117613632</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117613650</v>
+        <v>117613634</v>
       </c>
       <c r="B103" t="n">
         <v>80467</v>
@@ -12025,10 +12015,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>619568</v>
+        <v>619557</v>
       </c>
       <c r="R103" t="n">
-        <v>7215965</v>
+        <v>7215881</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12060,7 +12050,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12070,7 +12060,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12096,13 +12086,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613650</t>
+          <t>https://artportalen.se/Sighting/117613634</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117613760</v>
+        <v>117613650</v>
       </c>
       <c r="B104" t="n">
         <v>80467</v>
@@ -12137,10 +12127,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>619587</v>
+        <v>619568</v>
       </c>
       <c r="R104" t="n">
-        <v>7215747</v>
+        <v>7215965</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12172,7 +12162,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12182,7 +12172,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12208,16 +12198,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613760</t>
+          <t>https://artportalen.se/Sighting/117613650</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117613636</v>
+        <v>117613760</v>
       </c>
       <c r="B105" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12225,21 +12215,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12249,10 +12239,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>619504</v>
+        <v>619587</v>
       </c>
       <c r="R105" t="n">
-        <v>7215950</v>
+        <v>7215747</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12284,7 +12274,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12294,7 +12284,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12320,13 +12310,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613636</t>
+          <t>https://artportalen.se/Sighting/117613760</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117613641</v>
+        <v>117613636</v>
       </c>
       <c r="B106" t="n">
         <v>80468</v>
@@ -12361,10 +12351,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>619508</v>
+        <v>619504</v>
       </c>
       <c r="R106" t="n">
-        <v>7215964</v>
+        <v>7215950</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12396,7 +12386,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12406,7 +12396,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12432,13 +12422,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613641</t>
+          <t>https://artportalen.se/Sighting/117613636</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>117613643</v>
+        <v>117613641</v>
       </c>
       <c r="B107" t="n">
         <v>80468</v>
@@ -12473,10 +12463,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>619510</v>
+        <v>619508</v>
       </c>
       <c r="R107" t="n">
-        <v>7215959</v>
+        <v>7215964</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12508,7 +12498,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12518,7 +12508,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12544,13 +12534,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613643</t>
+          <t>https://artportalen.se/Sighting/117613641</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>117613649</v>
+        <v>117613643</v>
       </c>
       <c r="B108" t="n">
         <v>80468</v>
@@ -12585,10 +12575,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>619568</v>
+        <v>619510</v>
       </c>
       <c r="R108" t="n">
-        <v>7215965</v>
+        <v>7215959</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12620,7 +12610,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12630,7 +12620,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12656,13 +12646,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613649</t>
+          <t>https://artportalen.se/Sighting/117613643</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>117613714</v>
+        <v>117613649</v>
       </c>
       <c r="B109" t="n">
         <v>80468</v>
@@ -12697,10 +12687,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>619687</v>
+        <v>619568</v>
       </c>
       <c r="R109" t="n">
-        <v>7215792</v>
+        <v>7215965</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12732,7 +12722,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12742,7 +12732,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12768,13 +12758,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613714</t>
+          <t>https://artportalen.se/Sighting/117613649</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>117613721</v>
+        <v>117613714</v>
       </c>
       <c r="B110" t="n">
         <v>80468</v>
@@ -12809,10 +12799,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>619658</v>
+        <v>619687</v>
       </c>
       <c r="R110" t="n">
-        <v>7215775</v>
+        <v>7215792</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12844,7 +12834,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12854,7 +12844,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12880,13 +12870,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613721</t>
+          <t>https://artportalen.se/Sighting/117613714</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>117613732</v>
+        <v>117613721</v>
       </c>
       <c r="B111" t="n">
         <v>80468</v>
@@ -12921,10 +12911,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>619610</v>
+        <v>619658</v>
       </c>
       <c r="R111" t="n">
-        <v>7215808</v>
+        <v>7215775</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12956,7 +12946,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12966,7 +12956,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12992,16 +12982,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613732</t>
+          <t>https://artportalen.se/Sighting/117613721</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117613596</v>
+        <v>117613732</v>
       </c>
       <c r="B112" t="n">
-        <v>57950</v>
+        <v>80468</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13009,39 +12999,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>619674</v>
+        <v>619610</v>
       </c>
       <c r="R112" t="n">
-        <v>7215831</v>
+        <v>7215808</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13073,7 +13058,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13083,7 +13068,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13109,13 +13094,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613596</t>
+          <t>https://artportalen.se/Sighting/117613732</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>117613743</v>
+        <v>117613596</v>
       </c>
       <c r="B113" t="n">
         <v>57950</v>
@@ -13146,7 +13131,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13155,10 +13140,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>619606</v>
+        <v>619674</v>
       </c>
       <c r="R113" t="n">
-        <v>7215785</v>
+        <v>7215831</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13190,7 +13175,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13200,7 +13185,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13226,13 +13211,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613743</t>
+          <t>https://artportalen.se/Sighting/117613596</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117613756</v>
+        <v>117613743</v>
       </c>
       <c r="B114" t="n">
         <v>57950</v>
@@ -13263,7 +13248,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13272,10 +13257,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>619587</v>
+        <v>619606</v>
       </c>
       <c r="R114" t="n">
-        <v>7215759</v>
+        <v>7215785</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13307,7 +13292,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13317,7 +13302,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13343,13 +13328,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613756</t>
+          <t>https://artportalen.se/Sighting/117613743</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117613759</v>
+        <v>117613756</v>
       </c>
       <c r="B115" t="n">
         <v>57950</v>
@@ -13380,7 +13365,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13389,10 +13374,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>619588</v>
+        <v>619587</v>
       </c>
       <c r="R115" t="n">
-        <v>7215747</v>
+        <v>7215759</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13424,7 +13409,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13434,7 +13419,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13460,33 +13445,33 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613759</t>
+          <t>https://artportalen.se/Sighting/117613756</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>117613755</v>
+        <v>117613759</v>
       </c>
       <c r="B116" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -13506,10 +13491,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>619586</v>
+        <v>619588</v>
       </c>
       <c r="R116" t="n">
-        <v>7215778</v>
+        <v>7215747</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13541,7 +13526,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13551,7 +13536,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13577,13 +13562,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613755</t>
+          <t>https://artportalen.se/Sighting/117613759</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>117613763</v>
+        <v>117613755</v>
       </c>
       <c r="B117" t="n">
         <v>57953</v>
@@ -13623,10 +13608,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>619562</v>
+        <v>619586</v>
       </c>
       <c r="R117" t="n">
-        <v>7215748</v>
+        <v>7215778</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13658,7 +13643,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13668,7 +13653,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13694,46 +13679,41 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613763</t>
+          <t>https://artportalen.se/Sighting/117613755</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117613723</v>
+        <v>117613763</v>
       </c>
       <c r="B118" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -13745,10 +13725,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>619657</v>
+        <v>619562</v>
       </c>
       <c r="R118" t="n">
-        <v>7215776</v>
+        <v>7215748</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13780,7 +13760,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13790,12 +13770,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Fjädrar från död</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13821,16 +13796,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613723</t>
+          <t>https://artportalen.se/Sighting/117613763</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>117613683</v>
+        <v>117613723</v>
       </c>
       <c r="B119" t="n">
-        <v>58817</v>
+        <v>57141</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13838,16 +13813,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>208249</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -13855,9 +13830,15 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13866,10 +13847,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>619874</v>
+        <v>619657</v>
       </c>
       <c r="R119" t="n">
-        <v>7215912</v>
+        <v>7215776</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13901,7 +13882,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13911,7 +13892,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Fjädrar från död</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13937,51 +13923,55 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613683</t>
+          <t>https://artportalen.se/Sighting/117613723</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>117613667</v>
+        <v>117613683</v>
       </c>
       <c r="B120" t="n">
-        <v>41713</v>
+        <v>58817</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>215698</v>
+        <v>208249</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skogsfältmätare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Xanthorhoe annotinata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1839)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>619667</v>
+        <v>619874</v>
       </c>
       <c r="R120" t="n">
-        <v>7215919</v>
+        <v>7215912</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14013,7 +14003,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14023,7 +14013,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14049,13 +14039,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613667</t>
+          <t>https://artportalen.se/Sighting/117613683</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>117613697</v>
+        <v>117613667</v>
       </c>
       <c r="B121" t="n">
         <v>41713</v>
@@ -14083,26 +14073,17 @@
           <t>(Zetterstedt, 1839)</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>619758</v>
+        <v>619667</v>
       </c>
       <c r="R121" t="n">
-        <v>7215908</v>
+        <v>7215919</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14134,7 +14115,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14144,7 +14125,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14170,51 +14151,60 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613697</t>
+          <t>https://artportalen.se/Sighting/117613667</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>117613707</v>
+        <v>117613697</v>
       </c>
       <c r="B122" t="n">
-        <v>99035</v>
+        <v>41713</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219790</v>
+        <v>215698</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsfältmätare</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Xanthorhoe annotinata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Zetterstedt, 1839)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>619690</v>
+        <v>619758</v>
       </c>
       <c r="R122" t="n">
-        <v>7215909</v>
+        <v>7215908</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14246,7 +14236,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14256,7 +14246,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14282,16 +14272,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613707</t>
+          <t>https://artportalen.se/Sighting/117613697</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134045996</v>
+        <v>117613707</v>
       </c>
       <c r="B123" t="n">
-        <v>110023</v>
+        <v>99035</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14299,42 +14289,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220263</v>
+        <v>219790</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fjällskråp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Petasites frigidus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Skirliden, Skirliden, Ly lm</t>
+          <t>Skirträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>619906</v>
+        <v>619690</v>
       </c>
       <c r="R123" t="n">
-        <v>7215913</v>
+        <v>7215909</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14358,22 +14343,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>05:31</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>05:31</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14388,65 +14373,70 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Aron Dynesius</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Aron Dynesius</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134045996</t>
+          <t>https://artportalen.se/Sighting/117613707</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>117613595</v>
+        <v>134045996</v>
       </c>
       <c r="B124" t="n">
-        <v>99118</v>
+        <v>110023</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>220263</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskråp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Petasites frigidus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Skirträsket, Ly lm</t>
+          <t>Skirliden, Skirliden, Ly lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>619653</v>
+        <v>619906</v>
       </c>
       <c r="R124" t="n">
-        <v>7215831</v>
+        <v>7215913</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14470,22 +14460,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>05:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>05:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14500,24 +14490,24 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613595</t>
+          <t>https://artportalen.se/Sighting/134045996</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>117613597</v>
+        <v>117613595</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -14552,10 +14542,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>619624</v>
+        <v>619653</v>
       </c>
       <c r="R125" t="n">
-        <v>7215881</v>
+        <v>7215831</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14587,7 +14577,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14597,7 +14587,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14623,13 +14613,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613597</t>
+          <t>https://artportalen.se/Sighting/117613595</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>117613598</v>
+        <v>117613597</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -14664,10 +14654,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>619605</v>
+        <v>619624</v>
       </c>
       <c r="R126" t="n">
-        <v>7215860</v>
+        <v>7215881</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14699,7 +14689,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14709,7 +14699,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14735,13 +14725,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613598</t>
+          <t>https://artportalen.se/Sighting/117613597</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>117613604</v>
+        <v>117613598</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -14776,10 +14766,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>619557</v>
+        <v>619605</v>
       </c>
       <c r="R127" t="n">
-        <v>7215839</v>
+        <v>7215860</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14811,7 +14801,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14821,7 +14811,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14847,13 +14837,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613604</t>
+          <t>https://artportalen.se/Sighting/117613598</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>117613605</v>
+        <v>117613604</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -14888,10 +14878,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>619541</v>
+        <v>619557</v>
       </c>
       <c r="R128" t="n">
-        <v>7215850</v>
+        <v>7215839</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14923,7 +14913,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14933,7 +14923,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14959,13 +14949,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613605</t>
+          <t>https://artportalen.se/Sighting/117613604</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>117613606</v>
+        <v>117613605</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -15000,10 +14990,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>619549</v>
+        <v>619541</v>
       </c>
       <c r="R129" t="n">
-        <v>7215846</v>
+        <v>7215850</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15035,7 +15025,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15045,7 +15035,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15071,13 +15061,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613606</t>
+          <t>https://artportalen.se/Sighting/117613605</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>117613660</v>
+        <v>117613606</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -15112,10 +15102,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>619579</v>
+        <v>619549</v>
       </c>
       <c r="R130" t="n">
-        <v>7215923</v>
+        <v>7215846</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15147,7 +15137,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15157,7 +15147,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15183,13 +15173,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613660</t>
+          <t>https://artportalen.se/Sighting/117613606</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>117613664</v>
+        <v>117613660</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -15224,10 +15214,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>619606</v>
+        <v>619579</v>
       </c>
       <c r="R131" t="n">
-        <v>7215918</v>
+        <v>7215923</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15259,7 +15249,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15269,7 +15259,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15295,13 +15285,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613664</t>
+          <t>https://artportalen.se/Sighting/117613660</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>117613672</v>
+        <v>117613664</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -15336,10 +15326,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>619640</v>
+        <v>619606</v>
       </c>
       <c r="R132" t="n">
-        <v>7216000</v>
+        <v>7215918</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -15371,7 +15361,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15381,7 +15371,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15407,13 +15397,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613672</t>
+          <t>https://artportalen.se/Sighting/117613664</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>117613684</v>
+        <v>117613672</v>
       </c>
       <c r="B133" t="n">
         <v>99118</v>
@@ -15448,10 +15438,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>619857</v>
+        <v>619640</v>
       </c>
       <c r="R133" t="n">
-        <v>7215908</v>
+        <v>7216000</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -15483,7 +15473,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15493,7 +15483,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15519,13 +15509,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613684</t>
+          <t>https://artportalen.se/Sighting/117613672</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>117613688</v>
+        <v>117613684</v>
       </c>
       <c r="B134" t="n">
         <v>99118</v>
@@ -15560,10 +15550,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>619829</v>
+        <v>619857</v>
       </c>
       <c r="R134" t="n">
-        <v>7215911</v>
+        <v>7215908</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -15595,7 +15585,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15605,7 +15595,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15631,13 +15621,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613688</t>
+          <t>https://artportalen.se/Sighting/117613684</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>117613689</v>
+        <v>117613688</v>
       </c>
       <c r="B135" t="n">
         <v>99118</v>
@@ -15672,10 +15662,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>619811</v>
+        <v>619829</v>
       </c>
       <c r="R135" t="n">
-        <v>7215941</v>
+        <v>7215911</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15707,7 +15697,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15717,7 +15707,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15743,13 +15733,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613689</t>
+          <t>https://artportalen.se/Sighting/117613688</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>117613690</v>
+        <v>117613689</v>
       </c>
       <c r="B136" t="n">
         <v>99118</v>
@@ -15784,10 +15774,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>619785</v>
+        <v>619811</v>
       </c>
       <c r="R136" t="n">
-        <v>7215946</v>
+        <v>7215941</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15819,7 +15809,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15829,7 +15819,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15855,13 +15845,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613690</t>
+          <t>https://artportalen.se/Sighting/117613689</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>117613692</v>
+        <v>117613690</v>
       </c>
       <c r="B137" t="n">
         <v>99118</v>
@@ -15899,7 +15889,7 @@
         <v>619785</v>
       </c>
       <c r="R137" t="n">
-        <v>7215931</v>
+        <v>7215946</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15931,7 +15921,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15941,7 +15931,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15967,13 +15957,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613692</t>
+          <t>https://artportalen.se/Sighting/117613690</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>117613693</v>
+        <v>117613692</v>
       </c>
       <c r="B138" t="n">
         <v>99118</v>
@@ -16008,10 +15998,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>619772</v>
+        <v>619785</v>
       </c>
       <c r="R138" t="n">
-        <v>7215920</v>
+        <v>7215931</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16043,7 +16033,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16053,7 +16043,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16079,13 +16069,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613693</t>
+          <t>https://artportalen.se/Sighting/117613692</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>117613700</v>
+        <v>117613693</v>
       </c>
       <c r="B139" t="n">
         <v>99118</v>
@@ -16120,10 +16110,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>619743</v>
+        <v>619772</v>
       </c>
       <c r="R139" t="n">
-        <v>7215916</v>
+        <v>7215920</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16155,7 +16145,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16165,7 +16155,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16191,13 +16181,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613700</t>
+          <t>https://artportalen.se/Sighting/117613693</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>117613710</v>
+        <v>117613700</v>
       </c>
       <c r="B140" t="n">
         <v>99118</v>
@@ -16232,10 +16222,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>619715</v>
+        <v>619743</v>
       </c>
       <c r="R140" t="n">
-        <v>7215840</v>
+        <v>7215916</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -16267,7 +16257,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16277,7 +16267,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16303,13 +16293,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613710</t>
+          <t>https://artportalen.se/Sighting/117613700</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>117613719</v>
+        <v>117613710</v>
       </c>
       <c r="B141" t="n">
         <v>99118</v>
@@ -16344,10 +16334,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>619645</v>
+        <v>619715</v>
       </c>
       <c r="R141" t="n">
-        <v>7215791</v>
+        <v>7215840</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -16379,7 +16369,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16389,7 +16379,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16415,13 +16405,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613719</t>
+          <t>https://artportalen.se/Sighting/117613710</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>117613720</v>
+        <v>117613719</v>
       </c>
       <c r="B142" t="n">
         <v>99118</v>
@@ -16456,10 +16446,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>619652</v>
+        <v>619645</v>
       </c>
       <c r="R142" t="n">
-        <v>7215783</v>
+        <v>7215791</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16491,7 +16481,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16501,7 +16491,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16527,13 +16517,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613720</t>
+          <t>https://artportalen.se/Sighting/117613719</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>117613730</v>
+        <v>117613720</v>
       </c>
       <c r="B143" t="n">
         <v>99118</v>
@@ -16568,10 +16558,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>619610</v>
+        <v>619652</v>
       </c>
       <c r="R143" t="n">
-        <v>7215810</v>
+        <v>7215783</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16603,7 +16593,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16613,7 +16603,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16639,13 +16629,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613730</t>
+          <t>https://artportalen.se/Sighting/117613720</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>117613740</v>
+        <v>117613730</v>
       </c>
       <c r="B144" t="n">
         <v>99118</v>
@@ -16680,10 +16670,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>619604</v>
+        <v>619610</v>
       </c>
       <c r="R144" t="n">
-        <v>7215805</v>
+        <v>7215810</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16715,7 +16705,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16725,7 +16715,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16751,13 +16741,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613740</t>
+          <t>https://artportalen.se/Sighting/117613730</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>117613742</v>
+        <v>117613740</v>
       </c>
       <c r="B145" t="n">
         <v>99118</v>
@@ -16792,10 +16782,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>619596</v>
+        <v>619604</v>
       </c>
       <c r="R145" t="n">
-        <v>7215793</v>
+        <v>7215805</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16827,7 +16817,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16837,7 +16827,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16863,13 +16853,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613742</t>
+          <t>https://artportalen.se/Sighting/117613740</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>117613754</v>
+        <v>117613742</v>
       </c>
       <c r="B146" t="n">
         <v>99118</v>
@@ -16904,10 +16894,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>619582</v>
+        <v>619596</v>
       </c>
       <c r="R146" t="n">
-        <v>7215781</v>
+        <v>7215793</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16939,7 +16929,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16949,7 +16939,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16975,13 +16965,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613754</t>
+          <t>https://artportalen.se/Sighting/117613742</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>117613758</v>
+        <v>117613754</v>
       </c>
       <c r="B147" t="n">
         <v>99118</v>
@@ -17016,10 +17006,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>619578</v>
+        <v>619582</v>
       </c>
       <c r="R147" t="n">
-        <v>7215762</v>
+        <v>7215781</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17051,7 +17041,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17061,7 +17051,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17087,13 +17077,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613758</t>
+          <t>https://artportalen.se/Sighting/117613754</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>117613767</v>
+        <v>117613758</v>
       </c>
       <c r="B148" t="n">
         <v>99118</v>
@@ -17128,10 +17118,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>619544</v>
+        <v>619578</v>
       </c>
       <c r="R148" t="n">
-        <v>7215757</v>
+        <v>7215762</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -17163,7 +17153,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17173,7 +17163,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17199,38 +17189,38 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613767</t>
+          <t>https://artportalen.se/Sighting/117613758</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>117613708</v>
+        <v>117613767</v>
       </c>
       <c r="B149" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17240,10 +17230,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>619696</v>
+        <v>619544</v>
       </c>
       <c r="R149" t="n">
-        <v>7215892</v>
+        <v>7215757</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -17275,7 +17265,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17285,7 +17275,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17311,13 +17301,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613708</t>
+          <t>https://artportalen.se/Sighting/117613767</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>117613713</v>
+        <v>117613708</v>
       </c>
       <c r="B150" t="n">
         <v>106229</v>
@@ -17352,10 +17342,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>619685</v>
+        <v>619696</v>
       </c>
       <c r="R150" t="n">
-        <v>7215807</v>
+        <v>7215892</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -17387,7 +17377,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17397,7 +17387,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17423,13 +17413,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613713</t>
+          <t>https://artportalen.se/Sighting/117613708</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>117613718</v>
+        <v>117613713</v>
       </c>
       <c r="B151" t="n">
         <v>106229</v>
@@ -17464,10 +17454,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>619647</v>
+        <v>619685</v>
       </c>
       <c r="R151" t="n">
-        <v>7215800</v>
+        <v>7215807</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -17499,7 +17489,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17509,7 +17499,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17535,16 +17525,16 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613718</t>
+          <t>https://artportalen.se/Sighting/117613713</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>117613717</v>
+        <v>117613718</v>
       </c>
       <c r="B152" t="n">
-        <v>97983</v>
+        <v>106229</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17552,21 +17542,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17576,10 +17566,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>619690</v>
+        <v>619647</v>
       </c>
       <c r="R152" t="n">
-        <v>7215795</v>
+        <v>7215800</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -17611,7 +17601,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17621,7 +17611,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17647,13 +17637,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613717</t>
+          <t>https://artportalen.se/Sighting/117613718</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>117613741</v>
+        <v>117613717</v>
       </c>
       <c r="B153" t="n">
         <v>97983</v>
@@ -17688,10 +17678,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>619606</v>
+        <v>619690</v>
       </c>
       <c r="R153" t="n">
-        <v>7215798</v>
+        <v>7215795</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -17723,7 +17713,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17733,7 +17723,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17759,16 +17749,16 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613741</t>
+          <t>https://artportalen.se/Sighting/117613717</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>117613685</v>
+        <v>117613741</v>
       </c>
       <c r="B154" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17776,21 +17766,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17800,10 +17790,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>619851</v>
+        <v>619606</v>
       </c>
       <c r="R154" t="n">
-        <v>7215917</v>
+        <v>7215798</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17835,7 +17825,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17845,7 +17835,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17871,13 +17861,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613685</t>
+          <t>https://artportalen.se/Sighting/117613741</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>117613691</v>
+        <v>117613685</v>
       </c>
       <c r="B155" t="n">
         <v>99140</v>
@@ -17912,10 +17902,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>619783</v>
+        <v>619851</v>
       </c>
       <c r="R155" t="n">
-        <v>7215948</v>
+        <v>7215917</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17947,7 +17937,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17957,7 +17947,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17983,13 +17973,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613691</t>
+          <t>https://artportalen.se/Sighting/117613685</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>117613699</v>
+        <v>117613691</v>
       </c>
       <c r="B156" t="n">
         <v>99140</v>
@@ -18024,10 +18014,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>619743</v>
+        <v>619783</v>
       </c>
       <c r="R156" t="n">
-        <v>7215915</v>
+        <v>7215948</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -18059,7 +18049,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18069,7 +18059,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18095,13 +18085,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613699</t>
+          <t>https://artportalen.se/Sighting/117613691</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>117613716</v>
+        <v>117613699</v>
       </c>
       <c r="B157" t="n">
         <v>99140</v>
@@ -18136,10 +18126,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>619690</v>
+        <v>619743</v>
       </c>
       <c r="R157" t="n">
-        <v>7215797</v>
+        <v>7215915</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -18171,7 +18161,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18181,7 +18171,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18207,13 +18197,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613716</t>
+          <t>https://artportalen.se/Sighting/117613699</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>117613746</v>
+        <v>117613716</v>
       </c>
       <c r="B158" t="n">
         <v>99140</v>
@@ -18248,10 +18238,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>619573</v>
+        <v>619690</v>
       </c>
       <c r="R158" t="n">
-        <v>7215791</v>
+        <v>7215797</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -18283,7 +18273,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18293,7 +18283,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18319,16 +18309,16 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613746</t>
+          <t>https://artportalen.se/Sighting/117613716</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>117613600</v>
+        <v>117613746</v>
       </c>
       <c r="B159" t="n">
-        <v>104628</v>
+        <v>99140</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18336,21 +18326,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18360,10 +18350,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>619578</v>
+        <v>619573</v>
       </c>
       <c r="R159" t="n">
-        <v>7215828</v>
+        <v>7215791</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -18395,7 +18385,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18405,7 +18395,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18431,13 +18421,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613600</t>
+          <t>https://artportalen.se/Sighting/117613746</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>117613602</v>
+        <v>117613600</v>
       </c>
       <c r="B160" t="n">
         <v>104628</v>
@@ -18472,7 +18462,7 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>619572</v>
+        <v>619578</v>
       </c>
       <c r="R160" t="n">
         <v>7215828</v>
@@ -18543,13 +18533,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613602</t>
+          <t>https://artportalen.se/Sighting/117613600</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>117613609</v>
+        <v>117613602</v>
       </c>
       <c r="B161" t="n">
         <v>104628</v>
@@ -18584,10 +18574,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>619560</v>
+        <v>619572</v>
       </c>
       <c r="R161" t="n">
-        <v>7215847</v>
+        <v>7215828</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -18619,7 +18609,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18629,7 +18619,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18655,13 +18645,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613609</t>
+          <t>https://artportalen.se/Sighting/117613602</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>117613628</v>
+        <v>117613609</v>
       </c>
       <c r="B162" t="n">
         <v>104628</v>
@@ -18696,10 +18686,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>619547</v>
+        <v>619560</v>
       </c>
       <c r="R162" t="n">
-        <v>7215868</v>
+        <v>7215847</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -18731,7 +18721,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18741,7 +18731,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18767,13 +18757,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613628</t>
+          <t>https://artportalen.se/Sighting/117613609</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>117613629</v>
+        <v>117613628</v>
       </c>
       <c r="B163" t="n">
         <v>104628</v>
@@ -18808,10 +18798,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>619540</v>
+        <v>619547</v>
       </c>
       <c r="R163" t="n">
-        <v>7215870</v>
+        <v>7215868</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -18879,13 +18869,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613629</t>
+          <t>https://artportalen.se/Sighting/117613628</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>117613734</v>
+        <v>117613629</v>
       </c>
       <c r="B164" t="n">
         <v>104628</v>
@@ -18920,10 +18910,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>619607</v>
+        <v>619540</v>
       </c>
       <c r="R164" t="n">
-        <v>7215813</v>
+        <v>7215870</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -18955,7 +18945,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18965,7 +18955,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18991,13 +18981,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613734</t>
+          <t>https://artportalen.se/Sighting/117613629</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>117613752</v>
+        <v>117613734</v>
       </c>
       <c r="B165" t="n">
         <v>104628</v>
@@ -19032,10 +19022,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>619576</v>
+        <v>619607</v>
       </c>
       <c r="R165" t="n">
-        <v>7215783</v>
+        <v>7215813</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19067,7 +19057,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19077,7 +19067,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19103,16 +19093,16 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117613752</t>
+          <t>https://artportalen.se/Sighting/117613734</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>117613762</v>
+        <v>117613752</v>
       </c>
       <c r="B166" t="n">
-        <v>101228</v>
+        <v>104628</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19120,16 +19110,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -19144,10 +19134,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>619572</v>
+        <v>619576</v>
       </c>
       <c r="R166" t="n">
-        <v>7215766</v>
+        <v>7215783</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -19179,7 +19169,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19189,7 +19179,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19214,6 +19204,118 @@
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117613752</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>117613762</v>
+      </c>
+      <c r="B167" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Skirträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>619572</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7215766</v>
+      </c>
+      <c r="S167" t="n">
+        <v>25</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/117613762</t>
         </is>
@@ -19386,6 +19488,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92701</v>
+        <v>92703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92703</v>
+        <v>92716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92718</v>
+        <v>92721</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92721</v>
+        <v>92731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92732</v>
+        <v>92735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92737</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92754</v>
+        <v>92755</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92755</v>
+        <v>92758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 17199-2024 artfynd.xlsx
+++ b/artfynd/A 17199-2024 artfynd.xlsx
@@ -3146,7 +3146,7 @@
         <v>137152785</v>
       </c>
       <c r="B24" t="n">
-        <v>92758</v>
+        <v>92762</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
